--- a/Ledoit_Wolf_Results.xlsx
+++ b/Ledoit_Wolf_Results.xlsx
@@ -33,6 +33,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="d_hat" sheetId="24" state="visible" r:id="rId24"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sigma_NLS" sheetId="25" state="visible" r:id="rId25"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eigenvalues_NLS" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mu_vec" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Custom_Model_Weights" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Custom_Model_Summary" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9107,7 +9110,7 @@
         <v>46266</v>
       </c>
       <c r="B173" t="n">
-        <v>7650.5</v>
+        <v>7764.64014</v>
       </c>
     </row>
   </sheetData>
@@ -10501,7 +10504,7 @@
         <v>46266</v>
       </c>
       <c r="B172" t="n">
-        <v>-0.00464</v>
+        <v>0.01021</v>
       </c>
     </row>
   </sheetData>
@@ -17075,7 +17078,7 @@
         <v>-0.07506</v>
       </c>
       <c r="L172" t="n">
-        <v>-0.00464</v>
+        <v>0.01021</v>
       </c>
     </row>
   </sheetData>
@@ -18469,7 +18472,7 @@
         <v>46266</v>
       </c>
       <c r="B172" t="n">
-        <v>-0.00464</v>
+        <v>0.01021</v>
       </c>
     </row>
   </sheetData>
@@ -18520,7 +18523,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00179</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="5">
@@ -18540,7 +18543,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00277</v>
+        <v>0.00276</v>
       </c>
     </row>
     <row r="7">
@@ -18550,7 +18553,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00191</v>
+        <v>0.00192</v>
       </c>
     </row>
     <row r="8">
@@ -18580,7 +18583,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00221</v>
+        <v>0.00223</v>
       </c>
     </row>
     <row r="11">
@@ -18590,7 +18593,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.00075</v>
+        <v>0.00074</v>
       </c>
     </row>
   </sheetData>
@@ -18621,7 +18624,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.17195</v>
+        <v>1.17522</v>
       </c>
     </row>
     <row r="3">
@@ -18631,7 +18634,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.98044</v>
+        <v>0.97888</v>
       </c>
     </row>
     <row r="4">
@@ -18641,7 +18644,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.11234</v>
+        <v>1.11379</v>
       </c>
     </row>
     <row r="5">
@@ -18651,7 +18654,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.34702</v>
+        <v>1.34577</v>
       </c>
     </row>
     <row r="6">
@@ -18661,7 +18664,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.71501</v>
+        <v>1.71444</v>
       </c>
     </row>
     <row r="7">
@@ -18671,7 +18674,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.1809</v>
+        <v>1.18945</v>
       </c>
     </row>
     <row r="8">
@@ -18681,7 +18684,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.95697</v>
+        <v>0.95704</v>
       </c>
     </row>
     <row r="9">
@@ -18691,7 +18694,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.79353</v>
+        <v>1.79214</v>
       </c>
     </row>
     <row r="10">
@@ -18701,7 +18704,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.37106</v>
+        <v>1.38293</v>
       </c>
     </row>
     <row r="11">
@@ -18711,7 +18714,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.46184</v>
+        <v>0.45727</v>
       </c>
     </row>
   </sheetData>
@@ -18742,7 +18745,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00362</v>
+        <v>0.00361</v>
       </c>
     </row>
     <row r="3">
@@ -18752,7 +18755,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00274</v>
+        <v>0.00275</v>
       </c>
     </row>
     <row r="4">
@@ -18772,7 +18775,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00457</v>
+        <v>0.00458</v>
       </c>
     </row>
     <row r="6">
@@ -18782,7 +18785,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00974</v>
+        <v>0.00975</v>
       </c>
     </row>
     <row r="7">
@@ -18792,7 +18795,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0095</v>
+        <v>0.009469999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -18812,7 +18815,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02754</v>
+        <v>0.02755</v>
       </c>
     </row>
     <row r="10">
@@ -18822,7 +18825,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01458</v>
+        <v>0.01453</v>
       </c>
     </row>
     <row r="11">
@@ -18914,16 +18917,16 @@
         <v>0.00185</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0021</v>
+        <v>0.00211</v>
       </c>
       <c r="E2" t="n">
         <v>0.00255</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00324</v>
+        <v>0.00325</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00223</v>
+        <v>0.00225</v>
       </c>
       <c r="H2" t="n">
         <v>0.00181</v>
@@ -18932,7 +18935,7 @@
         <v>0.00339</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00259</v>
+        <v>0.00262</v>
       </c>
       <c r="K2" t="n">
         <v>0.00087</v>
@@ -18954,25 +18957,25 @@
         <v>0.00176</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00213</v>
+        <v>0.00212</v>
       </c>
       <c r="F3" t="n">
         <v>0.00271</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00187</v>
+        <v>0.00188</v>
       </c>
       <c r="H3" t="n">
         <v>0.00151</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00284</v>
+        <v>0.00283</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00217</v>
+        <v>0.00218</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00073</v>
+        <v>0.00072</v>
       </c>
     </row>
     <row r="4">
@@ -18982,7 +18985,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0021</v>
+        <v>0.00211</v>
       </c>
       <c r="C4" t="n">
         <v>0.00176</v>
@@ -18997,7 +19000,7 @@
         <v>0.00308</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00212</v>
+        <v>0.00214</v>
       </c>
       <c r="H4" t="n">
         <v>0.00172</v>
@@ -19006,10 +19009,10 @@
         <v>0.00322</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00246</v>
+        <v>0.00248</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00083</v>
+        <v>0.00082</v>
       </c>
     </row>
     <row r="5">
@@ -19022,7 +19025,7 @@
         <v>0.00255</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00213</v>
+        <v>0.00212</v>
       </c>
       <c r="D5" t="n">
         <v>0.00242</v>
@@ -19031,22 +19034,22 @@
         <v>0.0075</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00373</v>
+        <v>0.00372</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00257</v>
+        <v>0.00258</v>
       </c>
       <c r="H5" t="n">
         <v>0.00208</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0039</v>
+        <v>0.00389</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00298</v>
+        <v>0.003</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001</v>
+        <v>0.00099</v>
       </c>
     </row>
     <row r="6">
@@ -19056,7 +19059,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00324</v>
+        <v>0.00325</v>
       </c>
       <c r="C6" t="n">
         <v>0.00271</v>
@@ -19065,25 +19068,25 @@
         <v>0.00308</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00373</v>
+        <v>0.00372</v>
       </c>
       <c r="F6" t="n">
         <v>0.01449</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00327</v>
+        <v>0.00329</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00265</v>
+        <v>0.00264</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00496</v>
+        <v>0.00495</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00379</v>
+        <v>0.00382</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00128</v>
+        <v>0.00126</v>
       </c>
     </row>
     <row r="7">
@@ -19093,31 +19096,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00223</v>
+        <v>0.00225</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00187</v>
+        <v>0.00188</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00212</v>
+        <v>0.00214</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00257</v>
+        <v>0.00258</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00327</v>
+        <v>0.00329</v>
       </c>
       <c r="G7" t="n">
         <v>0.01175</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00182</v>
+        <v>0.00183</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00342</v>
+        <v>0.00344</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00261</v>
+        <v>0.00265</v>
       </c>
       <c r="K7" t="n">
         <v>0.00088</v>
@@ -19142,19 +19145,19 @@
         <v>0.00208</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00265</v>
+        <v>0.00264</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00182</v>
+        <v>0.00183</v>
       </c>
       <c r="H8" t="n">
         <v>0.008959999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00277</v>
+        <v>0.00276</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00212</v>
+        <v>0.00213</v>
       </c>
       <c r="K8" t="n">
         <v>0.00071</v>
@@ -19170,31 +19173,31 @@
         <v>0.00339</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00284</v>
+        <v>0.00283</v>
       </c>
       <c r="D9" t="n">
         <v>0.00322</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0039</v>
+        <v>0.00389</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00496</v>
+        <v>0.00495</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00342</v>
+        <v>0.00344</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00277</v>
+        <v>0.00276</v>
       </c>
       <c r="I9" t="n">
         <v>0.03273</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00397</v>
+        <v>0.00399</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00134</v>
+        <v>0.00132</v>
       </c>
     </row>
     <row r="10">
@@ -19204,28 +19207,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00259</v>
+        <v>0.00262</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00217</v>
+        <v>0.00218</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00246</v>
+        <v>0.00248</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00298</v>
+        <v>0.003</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00379</v>
+        <v>0.00382</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00261</v>
+        <v>0.00265</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00212</v>
+        <v>0.00213</v>
       </c>
       <c r="I10" t="n">
-        <v>0.00397</v>
+        <v>0.00399</v>
       </c>
       <c r="J10" t="n">
         <v>0.01761</v>
@@ -19244,16 +19247,16 @@
         <v>0.00087</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00073</v>
+        <v>0.00072</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00083</v>
+        <v>0.00082</v>
       </c>
       <c r="E11" t="n">
-        <v>0.001</v>
+        <v>0.00099</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00128</v>
+        <v>0.00126</v>
       </c>
       <c r="G11" t="n">
         <v>0.00088</v>
@@ -19262,7 +19265,7 @@
         <v>0.00071</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00134</v>
+        <v>0.00132</v>
       </c>
       <c r="J11" t="n">
         <v>0.00102</v>
@@ -25718,16 +25721,16 @@
         <v>0.00185</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0021</v>
+        <v>0.00211</v>
       </c>
       <c r="E2" t="n">
         <v>0.00255</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00324</v>
+        <v>0.00325</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00223</v>
+        <v>0.00225</v>
       </c>
       <c r="H2" t="n">
         <v>0.00181</v>
@@ -25736,7 +25739,7 @@
         <v>0.00339</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00259</v>
+        <v>0.00262</v>
       </c>
       <c r="K2" t="n">
         <v>0.00087</v>
@@ -25758,25 +25761,25 @@
         <v>0.00176</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00213</v>
+        <v>0.00212</v>
       </c>
       <c r="F3" t="n">
         <v>0.00271</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00187</v>
+        <v>0.00188</v>
       </c>
       <c r="H3" t="n">
         <v>0.00151</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00284</v>
+        <v>0.00283</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00217</v>
+        <v>0.00218</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00073</v>
+        <v>0.00072</v>
       </c>
     </row>
     <row r="4">
@@ -25786,7 +25789,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0021</v>
+        <v>0.00211</v>
       </c>
       <c r="C4" t="n">
         <v>0.00176</v>
@@ -25801,7 +25804,7 @@
         <v>0.00308</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00212</v>
+        <v>0.00214</v>
       </c>
       <c r="H4" t="n">
         <v>0.00172</v>
@@ -25810,10 +25813,10 @@
         <v>0.00322</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00246</v>
+        <v>0.00248</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00083</v>
+        <v>0.00082</v>
       </c>
     </row>
     <row r="5">
@@ -25826,7 +25829,7 @@
         <v>0.00255</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00213</v>
+        <v>0.00212</v>
       </c>
       <c r="D5" t="n">
         <v>0.00242</v>
@@ -25835,22 +25838,22 @@
         <v>0.0075</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00373</v>
+        <v>0.00372</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00257</v>
+        <v>0.00258</v>
       </c>
       <c r="H5" t="n">
         <v>0.00208</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0039</v>
+        <v>0.00389</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00298</v>
+        <v>0.003</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001</v>
+        <v>0.00099</v>
       </c>
     </row>
     <row r="6">
@@ -25860,7 +25863,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00324</v>
+        <v>0.00325</v>
       </c>
       <c r="C6" t="n">
         <v>0.00271</v>
@@ -25869,25 +25872,25 @@
         <v>0.00308</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00373</v>
+        <v>0.00372</v>
       </c>
       <c r="F6" t="n">
         <v>0.01449</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00327</v>
+        <v>0.00329</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00265</v>
+        <v>0.00264</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00496</v>
+        <v>0.00495</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00379</v>
+        <v>0.00382</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00128</v>
+        <v>0.00126</v>
       </c>
     </row>
     <row r="7">
@@ -25897,31 +25900,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00223</v>
+        <v>0.00225</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00187</v>
+        <v>0.00188</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00212</v>
+        <v>0.00214</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00257</v>
+        <v>0.00258</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00327</v>
+        <v>0.00329</v>
       </c>
       <c r="G7" t="n">
         <v>0.01175</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00182</v>
+        <v>0.00183</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00342</v>
+        <v>0.00344</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00261</v>
+        <v>0.00265</v>
       </c>
       <c r="K7" t="n">
         <v>0.00088</v>
@@ -25946,19 +25949,19 @@
         <v>0.00208</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00265</v>
+        <v>0.00264</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00182</v>
+        <v>0.00183</v>
       </c>
       <c r="H8" t="n">
         <v>0.008959999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00277</v>
+        <v>0.00276</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00212</v>
+        <v>0.00213</v>
       </c>
       <c r="K8" t="n">
         <v>0.00071</v>
@@ -25974,31 +25977,31 @@
         <v>0.00339</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00284</v>
+        <v>0.00283</v>
       </c>
       <c r="D9" t="n">
         <v>0.00322</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0039</v>
+        <v>0.00389</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00496</v>
+        <v>0.00495</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00342</v>
+        <v>0.00344</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00277</v>
+        <v>0.00276</v>
       </c>
       <c r="I9" t="n">
         <v>0.03273</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00397</v>
+        <v>0.00399</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00134</v>
+        <v>0.00132</v>
       </c>
     </row>
     <row r="10">
@@ -26008,28 +26011,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00259</v>
+        <v>0.00262</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00217</v>
+        <v>0.00218</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00246</v>
+        <v>0.00248</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00298</v>
+        <v>0.003</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00379</v>
+        <v>0.00382</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00261</v>
+        <v>0.00265</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00212</v>
+        <v>0.00213</v>
       </c>
       <c r="I10" t="n">
-        <v>0.00397</v>
+        <v>0.00399</v>
       </c>
       <c r="J10" t="n">
         <v>0.01761</v>
@@ -26048,16 +26051,16 @@
         <v>0.00087</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00073</v>
+        <v>0.00072</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00083</v>
+        <v>0.00082</v>
       </c>
       <c r="E11" t="n">
-        <v>0.001</v>
+        <v>0.00099</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00128</v>
+        <v>0.00126</v>
       </c>
       <c r="G11" t="n">
         <v>0.00088</v>
@@ -26066,7 +26069,7 @@
         <v>0.00071</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00134</v>
+        <v>0.00132</v>
       </c>
       <c r="J11" t="n">
         <v>0.00102</v>
@@ -27805,6 +27808,619 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mu_vec</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.01928</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.01849</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.02137</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.02194</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Nvidia</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.04548</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.02388</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.01822</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.04517</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01559</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Tencent</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.01734</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Sample (S)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Sigma_var</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Sigma_diag</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Sigma_corr</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Sigma_SF</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Sigma_NLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.04886</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.08026</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0659</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.11375</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.07722</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.04795</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.20033</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.17764</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.19587</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.23045</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.19993</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.20114</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.17479</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.16321</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.17693</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.21614</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.16767</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.17457</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.02243</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.03952</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Nvidia</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.15787</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.15225</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.15443</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.16808</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.15163</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.15757</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.04076</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.05742</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.04829</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.04078</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.06673</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.04029</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.16002</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.15541</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.15002</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.08431</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.07591000000000001</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.16134</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.05234</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.05468</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.05305</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02894</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.04775</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.05278</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Tencent</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.16503</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.15913</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.15551</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.09512</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.17363</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.16436</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Загвар</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Өгөөж</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Дисперс</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Хэлбэл</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Sharpe харьцаа</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Turnover_vs_S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sample (S)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.02468</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.05659</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.43602</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sigma_var</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.02468</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.00303</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.05503</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.10077</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sigma_diag</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.02468</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.00301</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.05485</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.05485</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sigma_corr</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.02468</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.05661</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.43589</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.33803</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sigma_SF</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.02468</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.00281</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.05298</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.46574</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.20489</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sigma_NLS</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.02468</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.00362</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.06014</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.41031</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.00516</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
